--- a/tests/gmx/Example_CEM/Example_output_files/PSD_Plot.xlsx
+++ b/tests/gmx/Example_CEM/Example_output_files/PSD_Plot.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PrO-VAT/tests/gmx/Example_CEM/Example_output_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PARSE/tests/gmx/Example_CEM/Example_output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC63CCB-C6C6-4233-8AE8-1FD8D1334734}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71DD74FB-55C2-4887-9AC1-246230110890}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GRO-GRO" sheetId="1" r:id="rId1"/>
@@ -71,16 +71,10 @@
     <t>Nonpolar Domain</t>
   </si>
   <si>
-    <t>PrO-VAT L = 1.0 A</t>
-  </si>
-  <si>
     <t>PoreBlazer L = 1.0 A</t>
   </si>
   <si>
     <t>min</t>
-  </si>
-  <si>
-    <t>PrO-VAT L = 0.5 A</t>
   </si>
   <si>
     <t>PoreBlazer L = 0.5 A</t>
@@ -104,25 +98,31 @@
     <t>24 Frames</t>
   </si>
   <si>
-    <t>PrO-VAT, 24 Frames</t>
-  </si>
-  <si>
-    <t>PrO-VAT, 1 Frame</t>
-  </si>
-  <si>
     <t>PoreBlazer, 1 Frame</t>
   </si>
   <si>
     <t>~35</t>
   </si>
   <si>
-    <t>PrO-VAT, 1 Frame, 8 (Random) Analyses</t>
-  </si>
-  <si>
     <t>~0.75</t>
   </si>
   <si>
     <t>~45</t>
+  </si>
+  <si>
+    <t>PARSE, 1 Frame</t>
+  </si>
+  <si>
+    <t>PARSE, 1 Frame, 8 (Random) Analyses</t>
+  </si>
+  <si>
+    <t>PARSE, 24 Frames</t>
+  </si>
+  <si>
+    <t>PARSE L = 1.0 A</t>
+  </si>
+  <si>
+    <t>PARSE L = 0.5 A</t>
   </si>
 </sst>
 </file>
@@ -1727,7 +1727,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT, 1 Frame</c:v>
+                  <c:v>PARSE, 1 Frame</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2234,7 +2234,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT, 1 Frame, 8 (Random) Analyses</c:v>
+                  <c:v>PARSE, 1 Frame, 8 (Random) Analyses</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3091,7 +3091,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT, 1 Frame</c:v>
+                  <c:v>PARSE, 1 Frame</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3598,7 +3598,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT, 1 Frame, 8 (Random) Analyses</c:v>
+                  <c:v>PARSE, 1 Frame, 8 (Random) Analyses</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6017,7 +6017,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT, 24 Frames</c:v>
+                  <c:v>PARSE, 24 Frames</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6524,7 +6524,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT, 1 Frame</c:v>
+                  <c:v>PARSE, 1 Frame</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7031,7 +7031,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT, 1 Frame, 8 (Random) Analyses</c:v>
+                  <c:v>PARSE, 1 Frame, 8 (Random) Analyses</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10650,7 +10650,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT L = 1.0 A</c:v>
+                  <c:v>PARSE L = 1.0 A</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11730,7 +11730,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PrO-VAT L = 0.5 A</c:v>
+                  <c:v>PARSE L = 0.5 A</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -17644,26 +17644,26 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="2"/>
       <c r="F1" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="K1" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="P1" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
@@ -17707,13 +17707,13 @@
       </c>
       <c r="P2" t="str">
         <f>A1</f>
-        <v>PrO-VAT, 1 Frame</v>
+        <v>PARSE, 1 Frame</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -17758,13 +17758,13 @@
       </c>
       <c r="P3" t="str">
         <f>F1</f>
-        <v>PrO-VAT, 1 Frame, 8 (Random) Analyses</v>
+        <v>PARSE, 1 Frame, 8 (Random) Analyses</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -17815,10 +17815,10 @@
         <v>PoreBlazer, 1 Frame</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -21533,13 +21533,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -21559,13 +21559,13 @@
       </c>
       <c r="F2" t="str">
         <f>A1</f>
-        <v>PrO-VAT, 24 Frames</v>
+        <v>PARSE, 24 Frames</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -22774,7 +22774,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -28112,28 +28112,28 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="3"/>
       <c r="F1" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="3"/>
       <c r="K1" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="3"/>
       <c r="P1" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
@@ -28141,31 +28141,31 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="K2" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="P2" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
       <c r="S2" s="5"/>
       <c r="U2" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
@@ -28221,13 +28221,13 @@
       </c>
       <c r="U3" t="str">
         <f>A2</f>
-        <v>PrO-VAT L = 1.0 A</v>
+        <v>PARSE L = 1.0 A</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -28288,10 +28288,10 @@
         <v>PoreBlazer L = 1.0 A</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -28353,13 +28353,13 @@
       </c>
       <c r="U5" t="str">
         <f>K2</f>
-        <v>PrO-VAT L = 0.5 A</v>
+        <v>PARSE L = 0.5 A</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="W5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -28424,10 +28424,10 @@
         <v>PoreBlazer L = 0.5 A</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="W6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
